--- a/results/model_table4.xlsx
+++ b/results/model_table4.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table4" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs_targets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perturbation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vfi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="projection" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +457,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>se_B</t>
+          <t>beta_capx</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>beta_ik</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>beta_zi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -479,18 +486,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.322</v>
+        <v>0.176</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00033</v>
+        <v>0.00053</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00067</v>
+        <v>-0.00327</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="I2" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -504,18 +517,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.343</v>
+        <v>0.184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00032</v>
+        <v>0.00052</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.00126</v>
+        <v>-0.00634</v>
       </c>
       <c r="F3" t="n">
-        <v>1e-05</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="I3" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -529,18 +548,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.367</v>
+        <v>0.192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00031</v>
+        <v>0.00052</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00178</v>
+        <v>-0.0092</v>
       </c>
       <c r="F4" t="n">
-        <v>1e-05</v>
+        <v>0.55</v>
       </c>
       <c r="G4" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="I4" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -554,18 +579,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.393</v>
+        <v>0.201</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00029</v>
+        <v>0.00051</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00223</v>
+        <v>-0.01187</v>
       </c>
       <c r="F5" t="n">
-        <v>1e-05</v>
+        <v>0.549</v>
       </c>
       <c r="G5" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="I5" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -579,18 +610,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.309</v>
+        <v>0.169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00031</v>
+        <v>0.0005</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00068</v>
+        <v>-0.0033</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="G6" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="I6" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -604,18 +641,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.33</v>
+        <v>0.176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003</v>
+        <v>0.00049</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0013</v>
+        <v>-0.00639</v>
       </c>
       <c r="F7" t="n">
-        <v>1e-05</v>
+        <v>0.544</v>
       </c>
       <c r="G7" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="I7" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -629,18 +672,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
+        <v>0.184</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00029</v>
+        <v>0.00049</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.00184</v>
+        <v>-0.00929</v>
       </c>
       <c r="F8" t="n">
-        <v>1e-05</v>
+        <v>0.544</v>
       </c>
       <c r="G8" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="I8" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -654,18 +703,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.378</v>
+        <v>0.194</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00028</v>
+        <v>0.00048</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0023</v>
+        <v>-0.01198</v>
       </c>
       <c r="F9" t="n">
-        <v>1e-05</v>
+        <v>0.543</v>
       </c>
       <c r="G9" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="I9" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -679,18 +734,24 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.315</v>
+        <v>0.169</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00031</v>
+        <v>0.0005</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00068</v>
+        <v>-0.0033</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="G10" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="I10" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -704,18 +765,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.337</v>
+        <v>0.176</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0003</v>
+        <v>0.00049</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.00128</v>
+        <v>-0.00639</v>
       </c>
       <c r="F11" t="n">
-        <v>1e-05</v>
+        <v>0.544</v>
       </c>
       <c r="G11" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="I11" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -729,18 +796,24 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.36</v>
+        <v>0.185</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00029</v>
+        <v>0.00049</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.00182</v>
+        <v>-0.00929</v>
       </c>
       <c r="F12" t="n">
-        <v>1e-05</v>
+        <v>0.544</v>
       </c>
       <c r="G12" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="I12" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -754,18 +827,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.386</v>
+        <v>0.194</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00028</v>
+        <v>0.00048</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00227</v>
+        <v>-0.01198</v>
       </c>
       <c r="F13" t="n">
-        <v>1e-05</v>
+        <v>0.543</v>
       </c>
       <c r="G13" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="I13" t="n">
         <v>199000</v>
       </c>
     </row>
@@ -835,22 +914,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3219582326995685</v>
+        <v>0.1760576837368958</v>
       </c>
       <c r="D2" t="n">
         <v>0.319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002958232699568464</v>
+        <v>-0.1429423162631042</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0006673651124567361</v>
+        <v>-0.003272946544602139</v>
       </c>
       <c r="G2" t="n">
         <v>-0.004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003332634887543264</v>
+        <v>0.0007270534553978614</v>
       </c>
     </row>
     <row r="3">
@@ -863,22 +942,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3432001367369984</v>
+        <v>0.1836976598732037</v>
       </c>
       <c r="D3" t="n">
         <v>0.344</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0007998632630015767</v>
+        <v>-0.1603023401267962</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001262111321658721</v>
+        <v>-0.006337878728481829</v>
       </c>
       <c r="G3" t="n">
         <v>-0.008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006737888678341279</v>
+        <v>0.001662121271518171</v>
       </c>
     </row>
     <row r="4">
@@ -891,22 +970,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3666204820446275</v>
+        <v>0.1920601864520562</v>
       </c>
       <c r="D4" t="n">
         <v>0.372</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005379517955372448</v>
+        <v>-0.1799398135479437</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.001783456643494861</v>
+        <v>-0.009202410463351336</v>
       </c>
       <c r="G4" t="n">
         <v>-0.011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009216543356505139</v>
+        <v>0.001797589536648663</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +998,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.392613126240346</v>
+        <v>0.2013331991037994</v>
       </c>
       <c r="D5" t="n">
         <v>0.404</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01138687375965403</v>
+        <v>-0.2026668008962006</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002229175449815519</v>
+        <v>-0.01187409173079725</v>
       </c>
       <c r="G5" t="n">
         <v>-0.014</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01177082455018448</v>
+        <v>0.00212590826920275</v>
       </c>
     </row>
     <row r="6">
@@ -947,22 +1026,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3091299443177955</v>
+        <v>0.1685029627295252</v>
       </c>
       <c r="D6" t="n">
         <v>0.319</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.009870055682204504</v>
+        <v>-0.1504970372704748</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.00068433513990112</v>
+        <v>-0.003301440704114347</v>
       </c>
       <c r="G6" t="n">
         <v>-0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00331566486009888</v>
+        <v>0.0006985592958856533</v>
       </c>
     </row>
     <row r="7">
@@ -975,22 +1054,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3297810343033191</v>
+        <v>0.1761155441462134</v>
       </c>
       <c r="D7" t="n">
         <v>0.344</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01421896569668085</v>
+        <v>-0.1678844558537866</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.001296516467351286</v>
+        <v>-0.00639430688303315</v>
       </c>
       <c r="G7" t="n">
         <v>-0.008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006703483532648715</v>
+        <v>0.00160569311696685</v>
       </c>
     </row>
     <row r="8">
@@ -1003,22 +1082,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3526791517139229</v>
+        <v>0.1844905413840154</v>
       </c>
       <c r="D8" t="n">
         <v>0.372</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01932084828607711</v>
+        <v>-0.1875094586159846</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001835159193080494</v>
+        <v>-0.009285916761460931</v>
       </c>
       <c r="G8" t="n">
         <v>-0.011</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009164840806919506</v>
+        <v>0.001714083238539069</v>
       </c>
     </row>
     <row r="9">
@@ -1031,22 +1110,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3780852947719037</v>
+        <v>0.1937424961974082</v>
       </c>
       <c r="D9" t="n">
         <v>0.404</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02591470522809636</v>
+        <v>-0.2102575038025918</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.002298174277272936</v>
+        <v>-0.0119845687575075</v>
       </c>
       <c r="G9" t="n">
         <v>-0.014</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01170182572272706</v>
+        <v>0.0020154312424925</v>
       </c>
     </row>
     <row r="10">
@@ -1059,22 +1138,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3153998436493631</v>
+        <v>0.1685081853300228</v>
       </c>
       <c r="D10" t="n">
         <v>0.319</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.003600156350636874</v>
+        <v>-0.1504918146699772</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0006789044253275683</v>
+        <v>-0.003301362568714571</v>
       </c>
       <c r="G10" t="n">
         <v>-0.004</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003321095574672432</v>
+        <v>0.0006986374312854286</v>
       </c>
     </row>
     <row r="11">
@@ -1087,22 +1166,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3365213833803106</v>
+        <v>0.1761209689744004</v>
       </c>
       <c r="D11" t="n">
         <v>0.344</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007478616619689349</v>
+        <v>-0.1678790310255996</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.001284978966201511</v>
+        <v>-0.00639413667859975</v>
       </c>
       <c r="G11" t="n">
         <v>-0.008</v>
       </c>
       <c r="H11" t="n">
-        <v>0.006715021033798489</v>
+        <v>0.00160586332140025</v>
       </c>
     </row>
     <row r="12">
@@ -1115,22 +1194,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.359935286720446</v>
+        <v>0.1845043825523361</v>
       </c>
       <c r="D12" t="n">
         <v>0.372</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.012064713279554</v>
+        <v>-0.1874956174476639</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.001816686201945888</v>
+        <v>-0.009285611968488008</v>
       </c>
       <c r="G12" t="n">
         <v>-0.011</v>
       </c>
       <c r="H12" t="n">
-        <v>0.009183313798054111</v>
+        <v>0.001714388031511992</v>
       </c>
     </row>
     <row r="13">
@@ -1143,475 +1222,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3858870673469969</v>
+        <v>0.1937464742500639</v>
       </c>
       <c r="D13" t="n">
         <v>0.404</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01811293265300312</v>
+        <v>-0.2102535257499361</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002272274163597893</v>
+        <v>-0.0119841862371854</v>
       </c>
       <c r="G13" t="n">
         <v>-0.014</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01172772583640211</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>gamma</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>beta_A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>se_A</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>beta_B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>se_B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>perturbation</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00033</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.00067</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>perturbation</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.00032</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.00126</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G3" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>perturbation</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.00031</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.00178</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>perturbation</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.00223</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G5" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>gamma</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>beta_A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>se_A</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>beta_B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>se_B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>vfi</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00031</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.00068</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>vfi</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.00128</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G3" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>vfi</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.00182</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>vfi</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.00028</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.00227</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G5" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>gamma</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>beta_A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>se_A</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>beta_B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>se_B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>projection</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00031</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.00068</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>projection</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G3" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>projection</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.00184</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>projection</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.00028</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G5" t="n">
-        <v>199000</v>
+        <v>0.002015813762814603</v>
       </c>
     </row>
   </sheetData>
